--- a/data/stats/supp_tables/yield-anova.xlsx
+++ b/data/stats/supp_tables/yield-anova.xlsx
@@ -11,6 +11,53 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>rowname</t>
+  </si>
+  <si>
+    <t>numDF</t>
+  </si>
+  <si>
+    <t>denDF</t>
+  </si>
+  <si>
+    <t>F-value</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>till_id</t>
+  </si>
+  <si>
+    <t>straw_id</t>
+  </si>
+  <si>
+    <t>cctrt_id</t>
+  </si>
+  <si>
+    <t>crop</t>
+  </si>
+  <si>
+    <t>till_id:straw_id</t>
+  </si>
+  <si>
+    <t>till_id:cctrt_id</t>
+  </si>
+  <si>
+    <t>straw_id:cctrt_id</t>
+  </si>
+  <si>
+    <t>till_id:straw_id:cctrt_id</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,38 +401,26 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rowname</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>numDF</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>denDF</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F-value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -400,11 +435,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>till_id</t>
-        </is>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -419,11 +452,9 @@
         <v>0.4836847181375379</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>straw_id</t>
-        </is>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -438,11 +469,9 @@
         <v>0.7855689476740824</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cctrt_id</t>
-        </is>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -457,11 +486,9 @@
         <v>0.003697177764845794</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>crop</t>
-        </is>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -476,11 +503,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>till_id:straw_id</t>
-        </is>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -495,11 +520,9 @@
         <v>0.1253744452956513</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>till_id:cctrt_id</t>
-        </is>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -514,11 +537,9 @@
         <v>0.6342069945629698</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>straw_id:cctrt_id</t>
-        </is>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -533,11 +554,9 @@
         <v>0.5691301215913369</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>till_id:straw_id:cctrt_id</t>
-        </is>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
       </c>
       <c r="B10">
         <v>8</v>
